--- a/database/event/5524/event_5524_evp_summary.xlsx
+++ b/database/event/5524/event_5524_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.751899999999999</v>
+        <v>9.694800000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>5.2477</v>
+        <v>5.2169</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5182</v>
+        <v>3.4185</v>
       </c>
       <c r="E2" t="n">
-        <v>9.751899999999999</v>
+        <v>9.694800000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0845</v>
+        <v>3.0274</v>
       </c>
       <c r="G2" t="n">
         <v>6.6674</v>
       </c>
       <c r="H2" t="n">
-        <v>3.0845</v>
+        <v>3.0274</v>
       </c>
       <c r="I2" t="n">
         <v>3.1569</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.5869</v>
+        <v>9.553100000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>5.1589</v>
+        <v>5.1407</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4515</v>
+        <v>3.362</v>
       </c>
       <c r="E3" t="n">
-        <v>9.5869</v>
+        <v>9.553100000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0385</v>
+        <v>3.0046</v>
       </c>
       <c r="G3" t="n">
         <v>6.5485</v>
       </c>
       <c r="H3" t="n">
-        <v>3.0385</v>
+        <v>3.0046</v>
       </c>
       <c r="I3" t="n">
         <v>3.0811</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.7598</v>
+        <v>5.7143</v>
       </c>
       <c r="C4" t="n">
-        <v>3.0995</v>
+        <v>3.075</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9055</v>
+        <v>1.8327</v>
       </c>
       <c r="E4" t="n">
-        <v>5.7598</v>
+        <v>5.7143</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0671</v>
+        <v>3.0216</v>
       </c>
       <c r="G4" t="n">
         <v>2.6927</v>
       </c>
       <c r="H4" t="n">
-        <v>3.0671</v>
+        <v>3.0216</v>
       </c>
       <c r="I4" t="n">
         <v>3.1246</v>
@@ -640,7 +640,7 @@
         <v>2.565</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5043</v>
+        <v>1.4551</v>
       </c>
       <c r="E5" t="n">
         <v>4.7667</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.4489</v>
+        <v>4.3992</v>
       </c>
       <c r="C6" t="n">
-        <v>2.394</v>
+        <v>2.3673</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3759</v>
+        <v>1.3087</v>
       </c>
       <c r="E6" t="n">
-        <v>4.4489</v>
+        <v>4.3992</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6827</v>
+        <v>2.633</v>
       </c>
       <c r="G6" t="n">
         <v>1.7662</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6827</v>
+        <v>2.633</v>
       </c>
       <c r="I6" t="n">
         <v>2.7457</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.0727</v>
+        <v>4.067</v>
       </c>
       <c r="C7" t="n">
-        <v>2.1916</v>
+        <v>2.1885</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2239</v>
+        <v>1.1764</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0727</v>
+        <v>4.067</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5322</v>
+        <v>1.5265</v>
       </c>
       <c r="G7" t="n">
         <v>2.5405</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5322</v>
+        <v>1.5265</v>
       </c>
       <c r="I7" t="n">
         <v>1.5393</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7865</v>
+        <v>3.7498</v>
       </c>
       <c r="C8" t="n">
-        <v>2.0376</v>
+        <v>2.0178</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1083</v>
+        <v>1.05</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7865</v>
+        <v>3.7498</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9844</v>
+        <v>1.9476</v>
       </c>
       <c r="G8" t="n">
         <v>1.8022</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9844</v>
+        <v>1.9476</v>
       </c>
       <c r="I8" t="n">
         <v>2.031</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5108</v>
+        <v>3.4853</v>
       </c>
       <c r="C9" t="n">
-        <v>1.8892</v>
+        <v>1.8755</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9969</v>
+        <v>0.9446</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5108</v>
+        <v>3.4853</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7183</v>
+        <v>1.6928</v>
       </c>
       <c r="G9" t="n">
         <v>1.7924</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7183</v>
+        <v>1.6928</v>
       </c>
       <c r="I9" t="n">
         <v>1.7505</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4397</v>
+        <v>3.4184</v>
       </c>
       <c r="C10" t="n">
-        <v>1.851</v>
+        <v>1.8395</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.918</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4397</v>
+        <v>3.4184</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1509</v>
+        <v>1.1296</v>
       </c>
       <c r="G10" t="n">
         <v>2.2888</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1509</v>
+        <v>1.1296</v>
       </c>
       <c r="I10" t="n">
         <v>1.178</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.3006</v>
+        <v>3.2963</v>
       </c>
       <c r="C11" t="n">
-        <v>1.7761</v>
+        <v>1.7738</v>
       </c>
       <c r="D11" t="n">
-        <v>0.912</v>
+        <v>0.8693</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3006</v>
+        <v>3.2963</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1611</v>
+        <v>1.1568</v>
       </c>
       <c r="G11" t="n">
         <v>2.1395</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1611</v>
+        <v>1.1568</v>
       </c>
       <c r="I11" t="n">
         <v>1.1665</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.2629</v>
+        <v>3.2354</v>
       </c>
       <c r="C12" t="n">
-        <v>1.7558</v>
+        <v>1.741</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8968</v>
+        <v>0.8451</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2629</v>
+        <v>3.2354</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8511</v>
+        <v>1.8236</v>
       </c>
       <c r="G12" t="n">
         <v>1.4118</v>
       </c>
       <c r="H12" t="n">
-        <v>1.8511</v>
+        <v>1.8236</v>
       </c>
       <c r="I12" t="n">
         <v>1.8858</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.1105</v>
+        <v>3.0595</v>
       </c>
       <c r="C13" t="n">
-        <v>1.6738</v>
+        <v>1.6464</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8352000000000001</v>
+        <v>0.775</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1105</v>
+        <v>3.0595</v>
       </c>
       <c r="F13" t="n">
-        <v>3.4366</v>
+        <v>3.3856</v>
       </c>
       <c r="G13" t="n">
         <v>-0.3261</v>
       </c>
       <c r="H13" t="n">
-        <v>3.4366</v>
+        <v>3.3856</v>
       </c>
       <c r="I13" t="n">
         <v>3.501</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.0723</v>
+        <v>3.0211</v>
       </c>
       <c r="C14" t="n">
-        <v>1.6533</v>
+        <v>1.6257</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8198</v>
+        <v>0.7597</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0723</v>
+        <v>3.0211</v>
       </c>
       <c r="F14" t="n">
-        <v>3.4505</v>
+        <v>3.3993</v>
       </c>
       <c r="G14" t="n">
         <v>-0.3782</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4505</v>
+        <v>3.3993</v>
       </c>
       <c r="I14" t="n">
         <v>3.5152</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.0223</v>
+        <v>3.0118</v>
       </c>
       <c r="C15" t="n">
-        <v>1.6264</v>
+        <v>1.6207</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7996</v>
+        <v>0.756</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0223</v>
+        <v>3.0118</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5535</v>
       </c>
       <c r="G15" t="n">
         <v>2.4583</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5535</v>
       </c>
       <c r="I15" t="n">
         <v>0.5772</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.5763</v>
+        <v>2.5507</v>
       </c>
       <c r="C16" t="n">
-        <v>1.3864</v>
+        <v>1.3726</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6194</v>
+        <v>0.5723</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5763</v>
+        <v>2.5507</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2959</v>
+        <v>2.2703</v>
       </c>
       <c r="G16" t="n">
         <v>0.2804</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2959</v>
+        <v>2.2703</v>
       </c>
       <c r="I16" t="n">
         <v>2.3282</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.549</v>
+        <v>2.5112</v>
       </c>
       <c r="C17" t="n">
-        <v>1.3717</v>
+        <v>1.3513</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6084000000000001</v>
+        <v>0.5566</v>
       </c>
       <c r="E17" t="n">
-        <v>2.549</v>
+        <v>2.5112</v>
       </c>
       <c r="F17" t="n">
-        <v>2.549</v>
+        <v>2.5112</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.549</v>
+        <v>2.5112</v>
       </c>
       <c r="I17" t="n">
         <v>2.5968</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.4955</v>
+        <v>2.4584</v>
       </c>
       <c r="C18" t="n">
-        <v>1.3429</v>
+        <v>1.3229</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5868</v>
+        <v>0.5355</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4955</v>
+        <v>2.4584</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4955</v>
+        <v>2.4584</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.4955</v>
+        <v>2.4584</v>
       </c>
       <c r="I18" t="n">
         <v>2.5422</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.409</v>
+        <v>2.3795</v>
       </c>
       <c r="C19" t="n">
-        <v>1.2963</v>
+        <v>1.2805</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5518</v>
+        <v>0.5041</v>
       </c>
       <c r="E19" t="n">
-        <v>2.409</v>
+        <v>2.3795</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5916</v>
+        <v>1.5621</v>
       </c>
       <c r="G19" t="n">
         <v>0.8174</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5916</v>
+        <v>1.5621</v>
       </c>
       <c r="I19" t="n">
         <v>1.629</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.2517</v>
+        <v>2.2119</v>
       </c>
       <c r="C20" t="n">
-        <v>1.2117</v>
+        <v>1.1903</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4883</v>
+        <v>0.4373</v>
       </c>
       <c r="E20" t="n">
-        <v>2.2517</v>
+        <v>2.2119</v>
       </c>
       <c r="F20" t="n">
-        <v>2.6816</v>
+        <v>2.6418</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4299</v>
       </c>
       <c r="H20" t="n">
-        <v>2.6816</v>
+        <v>2.6418</v>
       </c>
       <c r="I20" t="n">
         <v>2.7319</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.2189</v>
+        <v>2.1837</v>
       </c>
       <c r="C21" t="n">
-        <v>1.194</v>
+        <v>1.1751</v>
       </c>
       <c r="D21" t="n">
-        <v>0.475</v>
+        <v>0.4261</v>
       </c>
       <c r="E21" t="n">
-        <v>2.2189</v>
+        <v>2.1837</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3671</v>
+        <v>2.3319</v>
       </c>
       <c r="G21" t="n">
         <v>-0.1482</v>
       </c>
       <c r="H21" t="n">
-        <v>2.3671</v>
+        <v>2.3319</v>
       </c>
       <c r="I21" t="n">
         <v>2.4114</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.1921</v>
+        <v>2.1596</v>
       </c>
       <c r="C22" t="n">
-        <v>1.1796</v>
+        <v>1.1621</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4642</v>
+        <v>0.4165</v>
       </c>
       <c r="E22" t="n">
-        <v>2.1921</v>
+        <v>2.1596</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1921</v>
+        <v>2.1596</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.1921</v>
+        <v>2.1596</v>
       </c>
       <c r="I22" t="n">
         <v>2.2332</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.0657</v>
+        <v>2.0262</v>
       </c>
       <c r="C23" t="n">
-        <v>1.1116</v>
+        <v>1.0903</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4131</v>
+        <v>0.3633</v>
       </c>
       <c r="E23" t="n">
-        <v>2.0657</v>
+        <v>2.0262</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1315</v>
+        <v>2.092</v>
       </c>
       <c r="G23" t="n">
         <v>-0.0658</v>
       </c>
       <c r="H23" t="n">
-        <v>2.1315</v>
+        <v>2.092</v>
       </c>
       <c r="I23" t="n">
         <v>2.1816</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.7951</v>
+        <v>1.7537</v>
       </c>
       <c r="C24" t="n">
-        <v>0.966</v>
+        <v>0.9437</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3038</v>
+        <v>0.2548</v>
       </c>
       <c r="E24" t="n">
-        <v>1.7951</v>
+        <v>1.7537</v>
       </c>
       <c r="F24" t="n">
-        <v>2.7951</v>
+        <v>2.7537</v>
       </c>
       <c r="G24" t="n">
         <v>-1</v>
       </c>
       <c r="H24" t="n">
-        <v>2.7951</v>
+        <v>2.7537</v>
       </c>
       <c r="I24" t="n">
         <v>2.8475</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.6548</v>
+        <v>1.6363</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8905</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2471</v>
+        <v>0.208</v>
       </c>
       <c r="E25" t="n">
-        <v>1.6548</v>
+        <v>1.6363</v>
       </c>
       <c r="F25" t="n">
-        <v>1.6548</v>
+        <v>1.6363</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.6548</v>
+        <v>1.6363</v>
       </c>
       <c r="I25" t="n">
         <v>1.678</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.631</v>
+        <v>1.6068</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8777</v>
+        <v>0.8646</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2375</v>
+        <v>0.1962</v>
       </c>
       <c r="E26" t="n">
-        <v>1.631</v>
+        <v>1.6068</v>
       </c>
       <c r="F26" t="n">
-        <v>1.631</v>
+        <v>1.6068</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.631</v>
+        <v>1.6068</v>
       </c>
       <c r="I26" t="n">
         <v>1.6616</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.6188</v>
+        <v>1.5851</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8711</v>
+        <v>0.853</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2326</v>
+        <v>0.1876</v>
       </c>
       <c r="E27" t="n">
-        <v>1.6188</v>
+        <v>1.5851</v>
       </c>
       <c r="F27" t="n">
-        <v>1.8179</v>
+        <v>1.7842</v>
       </c>
       <c r="G27" t="n">
         <v>-0.1991</v>
       </c>
       <c r="H27" t="n">
-        <v>1.8179</v>
+        <v>1.7842</v>
       </c>
       <c r="I27" t="n">
         <v>1.8606</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.3555</v>
+        <v>1.3354</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7294</v>
+        <v>0.7186</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1262</v>
+        <v>0.0881</v>
       </c>
       <c r="E28" t="n">
-        <v>1.3555</v>
+        <v>1.3354</v>
       </c>
       <c r="F28" t="n">
-        <v>1.3555</v>
+        <v>1.3354</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.3555</v>
+        <v>1.3354</v>
       </c>
       <c r="I28" t="n">
         <v>1.3809</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.3376</v>
+        <v>1.3067</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7198</v>
+        <v>0.7032</v>
       </c>
       <c r="D29" t="n">
-        <v>0.119</v>
+        <v>0.0767</v>
       </c>
       <c r="E29" t="n">
-        <v>1.3376</v>
+        <v>1.3067</v>
       </c>
       <c r="F29" t="n">
-        <v>1.6692</v>
+        <v>1.6383</v>
       </c>
       <c r="G29" t="n">
         <v>-0.3316</v>
       </c>
       <c r="H29" t="n">
-        <v>1.6692</v>
+        <v>1.6383</v>
       </c>
       <c r="I29" t="n">
         <v>1.7084</v>
@@ -1790,7 +1790,7 @@
         <v>0.6935</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0992</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="E30" t="n">
         <v>1.2887</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.2697</v>
+        <v>1.2602</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6832</v>
+        <v>0.6781</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0916</v>
+        <v>0.0582</v>
       </c>
       <c r="E31" t="n">
-        <v>1.2697</v>
+        <v>1.2602</v>
       </c>
       <c r="F31" t="n">
-        <v>1.2697</v>
+        <v>1.2602</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.2697</v>
+        <v>1.2602</v>
       </c>
       <c r="I31" t="n">
         <v>1.2815</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.2041</v>
+        <v>1.1714</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6479</v>
+        <v>0.6304</v>
       </c>
       <c r="D32" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.0228</v>
       </c>
       <c r="E32" t="n">
-        <v>1.2041</v>
+        <v>1.1714</v>
       </c>
       <c r="F32" t="n">
-        <v>2.2041</v>
+        <v>2.1714</v>
       </c>
       <c r="G32" t="n">
         <v>-1</v>
       </c>
       <c r="H32" t="n">
-        <v>2.2041</v>
+        <v>2.1714</v>
       </c>
       <c r="I32" t="n">
         <v>2.2454</v>
@@ -1918,93 +1918,93 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.12</v>
+        <v>1.1113</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6027</v>
+        <v>0.598</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0311</v>
+        <v>-0.0012</v>
       </c>
       <c r="E33" t="n">
-        <v>1.12</v>
+        <v>1.1113</v>
       </c>
       <c r="F33" t="n">
-        <v>2.12</v>
+        <v>1.1113</v>
       </c>
       <c r="G33" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2.12</v>
+        <v>1.1113</v>
       </c>
       <c r="I33" t="n">
-        <v>2.1597</v>
+        <v>1.1207</v>
       </c>
       <c r="J33" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="L33" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.1597</v>
+        <v>1.1207</v>
       </c>
       <c r="N33" t="n">
-        <v>194</v>
+        <v>152</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.1155</v>
+        <v>1.0885</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6002999999999999</v>
+        <v>0.5857</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0293</v>
+        <v>-0.0103</v>
       </c>
       <c r="E34" t="n">
-        <v>1.1155</v>
+        <v>1.0885</v>
       </c>
       <c r="F34" t="n">
-        <v>1.1155</v>
+        <v>2.0885</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H34" t="n">
-        <v>1.1155</v>
+        <v>2.0885</v>
       </c>
       <c r="I34" t="n">
-        <v>1.1207</v>
+        <v>2.1597</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K34" t="n">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="M34" t="n">
-        <v>1.1207</v>
+        <v>1.1597</v>
       </c>
       <c r="N34" t="n">
-        <v>152</v>
+        <v>194</v>
       </c>
     </row>
     <row r="35">
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.0715</v>
+        <v>1.0675</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5766</v>
+        <v>0.5744</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0115</v>
+        <v>-0.0186</v>
       </c>
       <c r="E35" t="n">
-        <v>1.0715</v>
+        <v>1.0675</v>
       </c>
       <c r="F35" t="n">
-        <v>1.0715</v>
+        <v>1.0675</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.0715</v>
+        <v>1.0675</v>
       </c>
       <c r="I35" t="n">
         <v>1.0765</v>
@@ -2066,7 +2066,7 @@
         <v>0.5671</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0044</v>
+        <v>-0.024</v>
       </c>
       <c r="E36" t="n">
         <v>1.0539</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9772</v>
+        <v>0.9627</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5258</v>
+        <v>0.518</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0266</v>
+        <v>-0.0604</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9772</v>
+        <v>0.9627</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9772</v>
+        <v>0.9627</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9772</v>
+        <v>0.9627</v>
       </c>
       <c r="I37" t="n">
         <v>0.9955000000000001</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.9359</v>
+        <v>0.9151</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5036</v>
+        <v>0.4924</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0433</v>
+        <v>-0.0793</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9359</v>
+        <v>0.9151</v>
       </c>
       <c r="F38" t="n">
-        <v>1.4016</v>
+        <v>1.3808</v>
       </c>
       <c r="G38" t="n">
         <v>-0.4657</v>
       </c>
       <c r="H38" t="n">
-        <v>1.4016</v>
+        <v>1.3808</v>
       </c>
       <c r="I38" t="n">
         <v>1.4279</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7627</v>
+        <v>0.7599</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4104</v>
+        <v>0.4089</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1132</v>
+        <v>-0.1412</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7627</v>
+        <v>0.7599</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7627</v>
+        <v>0.7599</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.7627</v>
+        <v>0.7599</v>
       </c>
       <c r="I39" t="n">
         <v>0.7663</v>
@@ -2240,93 +2240,93 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7582</v>
+        <v>0.7366</v>
       </c>
       <c r="C40" t="n">
-        <v>0.408</v>
+        <v>0.3964</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1151</v>
+        <v>-0.1504</v>
       </c>
       <c r="E40" t="n">
-        <v>0.7582</v>
+        <v>0.7366</v>
       </c>
       <c r="F40" t="n">
-        <v>1.7582</v>
+        <v>0.7366</v>
       </c>
       <c r="G40" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.7582</v>
+        <v>0.7366</v>
       </c>
       <c r="I40" t="n">
-        <v>1.7912</v>
+        <v>0.7428</v>
       </c>
       <c r="J40" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L40" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.7911999999999999</v>
+        <v>0.7428</v>
       </c>
       <c r="N40" t="n">
-        <v>256</v>
+        <v>139</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.7321</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3979</v>
+        <v>0.394</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1227</v>
+        <v>-0.1522</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.7321</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7393999999999999</v>
+        <v>1.7321</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H41" t="n">
-        <v>0.7393999999999999</v>
+        <v>1.7321</v>
       </c>
       <c r="I41" t="n">
-        <v>0.7428</v>
+        <v>1.7912</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K41" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7428</v>
+        <v>0.7911999999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>139</v>
+        <v>256</v>
       </c>
     </row>
     <row r="42">
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.7049</v>
       </c>
       <c r="C42" t="n">
-        <v>0.3822</v>
+        <v>0.3793</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1345</v>
+        <v>-0.1631</v>
       </c>
       <c r="E42" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.7049</v>
       </c>
       <c r="F42" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.7049</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.7049</v>
       </c>
       <c r="I42" t="n">
         <v>0.7168</v>
@@ -2382,25 +2382,25 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5787</v>
+        <v>0.5733</v>
       </c>
       <c r="C43" t="n">
-        <v>0.3114</v>
+        <v>0.3085</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1876</v>
+        <v>-0.2155</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5787</v>
+        <v>0.5733</v>
       </c>
       <c r="F43" t="n">
-        <v>0.36</v>
+        <v>0.3546</v>
       </c>
       <c r="G43" t="n">
         <v>0.2187</v>
       </c>
       <c r="H43" t="n">
-        <v>0.36</v>
+        <v>0.3546</v>
       </c>
       <c r="I43" t="n">
         <v>0.3667</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5587</v>
+        <v>0.5327</v>
       </c>
       <c r="C44" t="n">
-        <v>0.3006</v>
+        <v>0.2867</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1957</v>
+        <v>-0.2317</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5587</v>
+        <v>0.5327</v>
       </c>
       <c r="F44" t="n">
-        <v>1.4045</v>
+        <v>1.3785</v>
       </c>
       <c r="G44" t="n">
         <v>-0.8458</v>
       </c>
       <c r="H44" t="n">
-        <v>1.4045</v>
+        <v>1.3785</v>
       </c>
       <c r="I44" t="n">
         <v>1.4374</v>
@@ -2474,25 +2474,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.3422</v>
+        <v>0.3403</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1841</v>
+        <v>0.1831</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2831</v>
+        <v>-0.3083</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3422</v>
+        <v>0.3403</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1029</v>
+        <v>0.101</v>
       </c>
       <c r="G45" t="n">
         <v>0.2393</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1029</v>
+        <v>0.101</v>
       </c>
       <c r="I45" t="n">
         <v>0.1053</v>
@@ -2520,25 +2520,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.1195</v>
+        <v>0.1192</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0643</v>
+        <v>0.0641</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3731</v>
+        <v>-0.3964</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1195</v>
+        <v>0.1192</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0173</v>
+        <v>0.017</v>
       </c>
       <c r="G46" t="n">
         <v>0.1022</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0173</v>
+        <v>0.017</v>
       </c>
       <c r="I46" t="n">
         <v>0.0176</v>
@@ -2566,25 +2566,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.1043</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0561</v>
+        <v>0.0473</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3792</v>
+        <v>-0.4089</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1043</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="F47" t="n">
-        <v>1.1043</v>
+        <v>1.0879</v>
       </c>
       <c r="G47" t="n">
         <v>-1</v>
       </c>
       <c r="H47" t="n">
-        <v>1.1043</v>
+        <v>1.0879</v>
       </c>
       <c r="I47" t="n">
         <v>1.125</v>
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.0842</v>
+        <v>0.0829</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0453</v>
+        <v>0.0446</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3873</v>
+        <v>-0.4109</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0842</v>
+        <v>0.0829</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0842</v>
+        <v>0.0829</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0842</v>
+        <v>0.0829</v>
       </c>
       <c r="I48" t="n">
         <v>0.0858</v>
@@ -2654,93 +2654,93 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.1296</v>
+        <v>-0.1278</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.0697</v>
+        <v>-0.0688</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4737</v>
+        <v>-0.4948</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.1296</v>
+        <v>-0.1278</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.1296</v>
+        <v>-0.1278</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.1296</v>
+        <v>-0.1278</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1302</v>
+        <v>-0.1322</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>140</v>
+        <v>228</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.1302</v>
+        <v>-0.1322</v>
       </c>
       <c r="N49" t="n">
-        <v>140</v>
+        <v>228</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.1298</v>
+        <v>-0.1291</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0698</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4738</v>
+        <v>-0.4953</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.1298</v>
+        <v>-0.1291</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.1298</v>
+        <v>-0.1291</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.1298</v>
+        <v>-0.1291</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1322</v>
+        <v>-0.1302</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>228</v>
+        <v>140</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.1322</v>
+        <v>-0.1302</v>
       </c>
       <c r="N50" t="n">
-        <v>228</v>
+        <v>140</v>
       </c>
     </row>
     <row r="51">
@@ -2750,25 +2750,25 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.1406</v>
+        <v>-0.138</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.0757</v>
+        <v>-0.0743</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4782</v>
+        <v>-0.4989</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.1406</v>
+        <v>-0.138</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.1406</v>
+        <v>-0.138</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.1406</v>
+        <v>-0.138</v>
       </c>
       <c r="I51" t="n">
         <v>-0.1439</v>
@@ -2796,25 +2796,25 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.1456</v>
+        <v>-0.1429</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0784</v>
+        <v>-0.0769</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4802</v>
+        <v>-0.5008</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.1456</v>
+        <v>-0.1429</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.1456</v>
+        <v>-0.1429</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.1456</v>
+        <v>-0.1429</v>
       </c>
       <c r="I52" t="n">
         <v>-0.149</v>
@@ -2842,25 +2842,25 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.1554</v>
+        <v>-0.1688</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.08359999999999999</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4841</v>
+        <v>-0.5112</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.1554</v>
+        <v>-0.1688</v>
       </c>
       <c r="F53" t="n">
-        <v>0.723</v>
+        <v>0.7096</v>
       </c>
       <c r="G53" t="n">
         <v>-0.8784</v>
       </c>
       <c r="H53" t="n">
-        <v>0.723</v>
+        <v>0.7096</v>
       </c>
       <c r="I53" t="n">
         <v>0.74</v>
@@ -2888,25 +2888,25 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.2326</v>
+        <v>-0.2362</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1252</v>
+        <v>-0.1271</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5153</v>
+        <v>-0.538</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.2326</v>
+        <v>-0.2362</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2426</v>
+        <v>0.239</v>
       </c>
       <c r="G54" t="n">
         <v>-0.4752</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2426</v>
+        <v>0.239</v>
       </c>
       <c r="I54" t="n">
         <v>0.2471</v>
@@ -2930,93 +2930,93 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>sdy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.3776</v>
+        <v>-0.3749</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.2032</v>
+        <v>-0.2017</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5739</v>
+        <v>-0.5933</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.3776</v>
+        <v>-0.3749</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.3776</v>
+        <v>-0.3749</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.3776</v>
+        <v>-0.3749</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3794</v>
+        <v>-0.3877</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.3794</v>
+        <v>-0.3877</v>
       </c>
       <c r="N55" t="n">
-        <v>152</v>
+        <v>196</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>sdy</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.3806</v>
+        <v>-0.3762</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.2048</v>
+        <v>-0.2024</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5750999999999999</v>
+        <v>-0.5938</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.3806</v>
+        <v>-0.3762</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.3806</v>
+        <v>-0.3762</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.3806</v>
+        <v>-0.3762</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3877</v>
+        <v>-0.3794</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>196</v>
+        <v>152</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.3877</v>
+        <v>-0.3794</v>
       </c>
       <c r="N56" t="n">
-        <v>196</v>
+        <v>152</v>
       </c>
     </row>
     <row r="57">
@@ -3026,25 +3026,25 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.3995</v>
+        <v>-0.3936</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.215</v>
+        <v>-0.2118</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5828</v>
+        <v>-0.6007</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.3995</v>
+        <v>-0.3936</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.3995</v>
+        <v>-0.3936</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.3995</v>
+        <v>-0.3936</v>
       </c>
       <c r="I57" t="n">
         <v>-0.407</v>
@@ -3072,25 +3072,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.4405</v>
+        <v>-0.4389</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.237</v>
+        <v>-0.2362</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5993000000000001</v>
+        <v>-0.6188</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.4405</v>
+        <v>-0.4389</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.4405</v>
+        <v>-0.4389</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.4405</v>
+        <v>-0.4389</v>
       </c>
       <c r="I58" t="n">
         <v>-0.4426</v>
@@ -3124,7 +3124,7 @@
         <v>-0.2931</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6414</v>
+        <v>-0.6609</v>
       </c>
       <c r="E59" t="n">
         <v>-0.5447</v>
@@ -3164,25 +3164,25 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.5885</v>
+        <v>-0.5863</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.3167</v>
+        <v>-0.3155</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6591</v>
+        <v>-0.6775</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.5885</v>
+        <v>-0.5863</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.5885</v>
+        <v>-0.5863</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.5885</v>
+        <v>-0.5863</v>
       </c>
       <c r="I60" t="n">
         <v>-0.5911999999999999</v>
@@ -3210,25 +3210,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.6529</v>
+        <v>-0.6504</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.3513</v>
+        <v>-0.35</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6851</v>
+        <v>-0.703</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.6529</v>
+        <v>-0.6504</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.6529</v>
+        <v>-0.6504</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.6529</v>
+        <v>-0.6504</v>
       </c>
       <c r="I61" t="n">
         <v>-0.6559</v>
@@ -3256,25 +3256,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.7014</v>
+        <v>-0.707</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.3774</v>
+        <v>-0.3804</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7047</v>
+        <v>-0.7256</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.7014</v>
+        <v>-0.707</v>
       </c>
       <c r="F62" t="n">
-        <v>0.3779</v>
+        <v>0.3723</v>
       </c>
       <c r="G62" t="n">
         <v>-1.0793</v>
       </c>
       <c r="H62" t="n">
-        <v>0.3779</v>
+        <v>0.3723</v>
       </c>
       <c r="I62" t="n">
         <v>0.385</v>
@@ -3308,7 +3308,7 @@
         <v>-0.4022</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7233000000000001</v>
+        <v>-0.7417</v>
       </c>
       <c r="E63" t="n">
         <v>-0.7474</v>
@@ -3348,25 +3348,25 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.9066</v>
+        <v>-0.8931</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.4879</v>
+        <v>-0.4806</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7876</v>
+        <v>-0.7997</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.9066</v>
+        <v>-0.8931</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.9066</v>
+        <v>-0.8931</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.9066</v>
+        <v>-0.8931</v>
       </c>
       <c r="I64" t="n">
         <v>-0.9236</v>
@@ -3394,25 +3394,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-0.9335</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.5042</v>
+        <v>-0.5023</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7999000000000001</v>
+        <v>-0.8158</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-0.9335</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-0.9335</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-0.9335</v>
       </c>
       <c r="I65" t="n">
         <v>-0.9414</v>
@@ -3446,7 +3446,7 @@
         <v>-0.529</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8185</v>
+        <v>-0.8355</v>
       </c>
       <c r="E66" t="n">
         <v>-0.983</v>
@@ -3492,7 +3492,7 @@
         <v>-0.5463</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8315</v>
+        <v>-0.8484</v>
       </c>
       <c r="E67" t="n">
         <v>-1.0152</v>
@@ -3532,25 +3532,25 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.0441</v>
+        <v>-1.0402</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.5618</v>
+        <v>-0.5598</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8431999999999999</v>
+        <v>-0.8583</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.0441</v>
+        <v>-1.0402</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.0441</v>
+        <v>-1.0402</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-1.0441</v>
+        <v>-1.0402</v>
       </c>
       <c r="I68" t="n">
         <v>-1.049</v>
@@ -3574,93 +3574,93 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.0473</v>
+        <v>-1.0435</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.5636</v>
+        <v>-0.5615</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8444</v>
+        <v>-0.8596</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.0473</v>
+        <v>-1.0435</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.0473</v>
+        <v>-1.0435</v>
       </c>
       <c r="G69" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.0473</v>
+        <v>-1.0435</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0482</v>
+        <v>-1.0523</v>
       </c>
       <c r="J69" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L69" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-1.0482</v>
+        <v>-1.0523</v>
       </c>
       <c r="N69" t="n">
-        <v>245</v>
+        <v>139</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.0474</v>
+        <v>-1.0466</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.5636</v>
+        <v>-0.5632</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8445</v>
+        <v>-0.8609</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.0474</v>
+        <v>-1.0466</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.0474</v>
+        <v>-0.0466</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.0474</v>
+        <v>-0.0466</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.0523</v>
+        <v>-0.0482</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K70" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="M70" t="n">
-        <v>-1.0523</v>
+        <v>-1.0482</v>
       </c>
       <c r="N70" t="n">
-        <v>139</v>
+        <v>245</v>
       </c>
     </row>
     <row r="71">
@@ -3670,25 +3670,25 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.0737</v>
+        <v>-1.0577</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.5778</v>
+        <v>-0.5692</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8551</v>
+        <v>-0.8653</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.0737</v>
+        <v>-1.0577</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.0737</v>
+        <v>-1.0577</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.0737</v>
+        <v>-1.0577</v>
       </c>
       <c r="I71" t="n">
         <v>-1.0938</v>
@@ -3716,25 +3716,25 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.1743</v>
+        <v>-1.1643</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.6319</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8958</v>
+        <v>-0.9078000000000001</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.1743</v>
+        <v>-1.1643</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.5399</v>
+        <v>-0.5299</v>
       </c>
       <c r="G72" t="n">
         <v>-0.6344</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.5399</v>
+        <v>-0.5299</v>
       </c>
       <c r="I72" t="n">
         <v>-0.5526</v>
@@ -3762,25 +3762,25 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.1894</v>
+        <v>-1.1718</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.64</v>
+        <v>-0.6306</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9019</v>
+        <v>-0.9108000000000001</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.1894</v>
+        <v>-1.1718</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.1894</v>
+        <v>-1.1718</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.1894</v>
+        <v>-1.1718</v>
       </c>
       <c r="I73" t="n">
         <v>-1.2117</v>
@@ -3808,25 +3808,25 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.2606</v>
+        <v>-1.2559</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.6784</v>
+        <v>-0.6758</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9306</v>
+        <v>-0.9443</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.2606</v>
+        <v>-1.2559</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.2606</v>
+        <v>-1.2559</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.2606</v>
+        <v>-1.2559</v>
       </c>
       <c r="I74" t="n">
         <v>-1.2665</v>
@@ -3854,25 +3854,25 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.5447</v>
+        <v>-1.5389</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.8312</v>
+        <v>-0.8280999999999999</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0454</v>
+        <v>-1.057</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.5447</v>
+        <v>-1.5389</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.5447</v>
+        <v>-1.5389</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.5447</v>
+        <v>-1.5389</v>
       </c>
       <c r="I75" t="n">
         <v>-1.5519</v>
@@ -3900,25 +3900,25 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.763</v>
+        <v>-1.7369</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.9487</v>
+        <v>-0.9347</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1336</v>
+        <v>-1.1359</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.763</v>
+        <v>-1.7369</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.763</v>
+        <v>-1.7369</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.763</v>
+        <v>-1.7369</v>
       </c>
       <c r="I76" t="n">
         <v>-1.7961</v>
@@ -3946,25 +3946,25 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.9907</v>
+        <v>-1.9833</v>
       </c>
       <c r="C77" t="n">
-        <v>-1.0712</v>
+        <v>-1.0673</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2256</v>
+        <v>-1.2341</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.9907</v>
+        <v>-1.9833</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.9907</v>
+        <v>-1.9833</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.9907</v>
+        <v>-1.9833</v>
       </c>
       <c r="I77" t="n">
         <v>-2</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.0408</v>
+        <v>-2.0172</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.0982</v>
+        <v>-1.0855</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2458</v>
+        <v>-1.2476</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.0408</v>
+        <v>-2.0172</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.2732</v>
+        <v>-1.2496</v>
       </c>
       <c r="G78" t="n">
         <v>-0.7675999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.2732</v>
+        <v>-1.2496</v>
       </c>
       <c r="I78" t="n">
         <v>-1.3031</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.1088</v>
+        <v>-2.1071</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.1348</v>
+        <v>-1.1339</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.2733</v>
+        <v>-1.2834</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.1088</v>
+        <v>-2.1071</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.1088</v>
+        <v>-0.1071</v>
       </c>
       <c r="G79" t="n">
         <v>-2</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.1088</v>
+        <v>-0.1071</v>
       </c>
       <c r="I79" t="n">
         <v>-0.1108</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.186</v>
+        <v>-2.1662</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.1763</v>
+        <v>-1.1657</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.3045</v>
+        <v>-1.3069</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.186</v>
+        <v>-2.1662</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.335</v>
+        <v>-1.3152</v>
       </c>
       <c r="G80" t="n">
         <v>-0.851</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.335</v>
+        <v>-1.3152</v>
       </c>
       <c r="I80" t="n">
         <v>-1.36</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.7241</v>
+        <v>-2.7036</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.4659</v>
+        <v>-1.4549</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.5218</v>
+        <v>-1.521</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.7241</v>
+        <v>-2.7036</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.1061</v>
+        <v>-1.0856</v>
       </c>
       <c r="G81" t="n">
         <v>-1.618</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.1061</v>
+        <v>-1.0856</v>
       </c>
       <c r="I81" t="n">
         <v>-1.1321</v>
@@ -4176,25 +4176,25 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-3.258</v>
+        <v>-3.2097</v>
       </c>
       <c r="C82" t="n">
-        <v>-1.7532</v>
+        <v>-1.7272</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.7375</v>
+        <v>-1.7227</v>
       </c>
       <c r="E82" t="n">
-        <v>-3.258</v>
+        <v>-3.2097</v>
       </c>
       <c r="F82" t="n">
-        <v>-3.258</v>
+        <v>-3.2097</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>-3.258</v>
+        <v>-3.2097</v>
       </c>
       <c r="I82" t="n">
         <v>-3.3191</v>
